--- a/3_Бюджетирование/Макеты/02/ВА_КонтекстныйПересчетИсходный.xlsx
+++ b/3_Бюджетирование/Макеты/02/ВА_КонтекстныйПересчетИсходный.xlsx
@@ -27,11 +27,11 @@
             <u val="none"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Бюджетирование1 (03.03.2026 18:15:45): 
+          <t>Бюджетирование1 (22.05.2026 6:16:57): 
 Первая ячейка
-Бюджетирование1 (03.03.2026 18:15:45): 
+Бюджетирование1 (22.05.2026 6:16:58): 
 Первая ячейка 2
-Бюджетирование1 (03.03.2026 18:15:47): 
+Бюджетирование1 (22.05.2026 6:17:03): 
 Первая ячейка 3</t>
         </r>
       </text>
@@ -44,7 +44,7 @@
             <u val="none"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Бюджетирование1 (03.03.2026 18:15:45): 
+          <t>Бюджетирование1 (22.05.2026 6:16:57): 
 Последняя ячейка</t>
         </r>
       </text>

--- a/3_Бюджетирование/Макеты/02/ВА_КонтекстныйПересчетИсходный.xlsx
+++ b/3_Бюджетирование/Макеты/02/ВА_КонтекстныйПересчетИсходный.xlsx
@@ -27,11 +27,11 @@
             <u val="none"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Бюджетирование1 (22.05.2026 6:16:57): 
+          <t>Бюджетирование1 (03.03.2026 18:15:45): 
 Первая ячейка
-Бюджетирование1 (22.05.2026 6:16:58): 
+Бюджетирование1 (03.03.2026 18:15:45): 
 Первая ячейка 2
-Бюджетирование1 (22.05.2026 6:17:03): 
+Бюджетирование1 (03.03.2026 18:15:47): 
 Первая ячейка 3</t>
         </r>
       </text>
@@ -44,7 +44,7 @@
             <u val="none"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Бюджетирование1 (22.05.2026 6:16:57): 
+          <t>Бюджетирование1 (03.03.2026 18:15:45): 
 Последняя ячейка</t>
         </r>
       </text>

--- a/3_Бюджетирование/Макеты/02/ВА_КонтекстныйПересчетИсходный.xlsx
+++ b/3_Бюджетирование/Макеты/02/ВА_КонтекстныйПересчетИсходный.xlsx
@@ -27,11 +27,11 @@
             <u val="none"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Бюджетирование1 (03.03.2026 18:15:45): 
+          <t>Бюджетирование1 (26.05.2026 5:49:44): 
 Первая ячейка
-Бюджетирование1 (03.03.2026 18:15:45): 
+Бюджетирование1 (26.05.2026 5:49:45): 
 Первая ячейка 2
-Бюджетирование1 (03.03.2026 18:15:47): 
+Бюджетирование1 (26.05.2026 5:49:50): 
 Первая ячейка 3</t>
         </r>
       </text>
@@ -44,7 +44,7 @@
             <u val="none"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Бюджетирование1 (03.03.2026 18:15:45): 
+          <t>Бюджетирование1 (26.05.2026 5:49:45): 
 Последняя ячейка</t>
         </r>
       </text>
